--- a/artfynd/A 41228-2025 artfynd.xlsx
+++ b/artfynd/A 41228-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128582460</v>
       </c>
       <c r="B2" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>128582472</v>
       </c>
       <c r="B3" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41228-2025 artfynd.xlsx
+++ b/artfynd/A 41228-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128582460</v>
       </c>
       <c r="B2" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>128582472</v>
       </c>
       <c r="B3" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41228-2025 artfynd.xlsx
+++ b/artfynd/A 41228-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128582460</v>
       </c>
       <c r="B2" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>128582472</v>
       </c>
       <c r="B3" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41228-2025 artfynd.xlsx
+++ b/artfynd/A 41228-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128582460</v>
       </c>
       <c r="B2" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>128582472</v>
       </c>
       <c r="B3" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41228-2025 artfynd.xlsx
+++ b/artfynd/A 41228-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128582460</v>
+        <v>128582425</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>58114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548676</v>
+        <v>548597</v>
       </c>
       <c r="R2" t="n">
-        <v>6321283</v>
+        <v>6321323</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -761,7 +761,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,10 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128582472</v>
+        <v>128582460</v>
       </c>
       <c r="B3" t="n">
-        <v>57883</v>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548739</v>
+        <v>548676</v>
       </c>
       <c r="R3" t="n">
-        <v>6321411</v>
+        <v>6321283</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,6 +918,129 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128582472</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>548739</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6321411</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41228-2025 artfynd.xlsx
+++ b/artfynd/A 41228-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -795,6 +800,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128582425</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -918,6 +928,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128582460</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1041,8 +1056,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128582472</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>